--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="R4e52409c12e945a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_TARIFAS_ANAC" sheetId="2" r:id="Recabf11c4c7542f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_GOOGLE_FLIGHTS" sheetId="3" r:id="Rea0a0b4551da45ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCENTIVOS_MEDIDAS" sheetId="4" r:id="R3fd7e880c6684fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSARIO_METODOLOGIA" sheetId="5" r:id="R60aaa8e854394e6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="6" r:id="R5c19e2636f1b49da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="R05cde3119ab64bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_TARIFAS_ANAC" sheetId="2" r:id="Rae58469db8494a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_GOOGLE_FLIGHTS" sheetId="3" r:id="R242b7e3558e94218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCENTIVOS_MEDIDAS" sheetId="4" r:id="R35ea366599a74733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSARIO_METODOLOGIA" sheetId="5" r:id="R0394b19f902342a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="6" r:id="Rfc895460c20946c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -95,6 +95,11 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -103,7 +108,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -189,6 +194,14 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -14643,7 +14656,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb054c9622b44e79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf32fc2999cc47ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29519,7 +29532,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3409262b8247b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re90750637d034bf5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29528,32 +29541,36 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="82" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="11" t="str">
+      <x:c r="A1" s="43" t="str">
         <x:v>Medida_Fator</x:v>
       </x:c>
-      <x:c r="B1" s="11" t="str">
+      <x:c r="B1" s="43" t="str">
         <x:v>Inicio_Periodo</x:v>
       </x:c>
-      <x:c r="C1" s="11" t="str">
+      <x:c r="C1" s="43" t="str">
         <x:v>Abrangencia</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="D1" s="43" t="str">
         <x:v>Efeito_Esperado</x:v>
       </x:c>
-      <x:c r="E1" s="11" t="str">
+      <x:c r="E1" s="43" t="str">
         <x:v>Detalhe</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="str">
+      <x:c r="F1" s="43" t="str">
         <x:v>Fonte_URL</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>Como_Impacta</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -29573,6 +29590,9 @@
         <x:v>Incentivo estadual para companhias que cumpram requisitos ligados ao aumento da conectividade e ao hub no Salgado Filho.</x:v>
       </x:c>
       <x:c r="F2" s="16" t="str"/>
+      <x:c r="G2" s="16" t="str">
+        <x:v>Reduz a carga tributária sobre o combustível para empresas que atendam às condições do programa. Como o QAV é um dos principais custos operacionais das aéreas, a medida pode diminuir a pressão de custos e tornar novas frequências ou rotas para Porto Alegre mais viáveis. O efeito sobre a tarifa ao passageiro é indireto: depende de concorrência, demanda e de quanto da economia é repassada ao preço.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="16" t="str">
@@ -29588,115 +29608,264 @@
         <x:v>↓ Custos das aéreas</x:v>
       </x:c>
       <x:c r="E3" s="16" t="str">
-        <x:v>Governo Federal zerou temporariamente os tributos sobre o querosene de aviação.</x:v>
+        <x:v>Governo Federal zerou temporariamente os tributos sobre o querosene de aviação; estimativa inicial de redução de cerca de R$ 0,07/litro.</x:v>
       </x:c>
       <x:c r="F3" s="16" t="str"/>
+      <x:c r="G3" s="16" t="str">
+        <x:v>A desoneração reduz temporariamente o custo de aquisição do combustível em todo o país. Isso pode aliviar a necessidade de reajustes de tarifas e ajudar a preservar oferta e capacidade, mas não garante queda automática dos preços, porque a formação tarifária também depende de demanda, concorrência, câmbio, ocupação e estratégia comercial.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="16" t="str">
+        <x:v>Linha de financiamento FNAC</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Abr/2026</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>↓ Pressão financeira</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Crédito para o setor aéreo diante da alta do QAV. O pacote aprovado chegou a R$ 8 bilhões em financiamento.</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str"/>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Aumenta o acesso das companhias a financiamento e liquidez em um período de custos elevados. O impacto é principalmente financeiro: reduz pressão de caixa e pode evitar cortes de malha ou repasses imediatos de custos. Não entra diretamente no cálculo da tarifa ANAC e seu efeito sobre o preço é indireto.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16" t="str">
+        <x:v>Crédito para capital de giro</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>Abr/2026</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>↓ Pressão financeira</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>Linha voltada às empresas aéreas para amenizar o aumento dos custos operacionais.</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str"/>
+      <x:c r="G5" s="16" t="str">
+        <x:v>Melhora o caixa disponível para despesas operacionais de curto prazo. Ao reduzir restrições financeiras, pode diminuir a necessidade de respostas abruptas, como redução de frequências ou aumentos emergenciais de preço. O benefício tarifário, porém, depende da decisão comercial de cada companhia.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="16" t="str">
+        <x:v>Postergação de tarifas de navegação aérea</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>↓ Pressão de caixa</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>Empresas puderam adiar determinados pagamentos de tarifas de navegação aérea para dezembro.</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="str"/>
+      <x:c r="G6" s="16" t="str">
+        <x:v>Não reduz necessariamente o custo total devido pelas empresas, mas desloca pagamentos para frente e melhora o fluxo de caixa no curto prazo. Isso pode aliviar a pressão financeira em momentos de alta de custos e ajudar a sustentar operações, sem representar redução direta ou automática da tarifa paga pelo passageiro.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="16" t="str">
+        <x:v>Parcelamento do reajuste do QAV</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="str">
+        <x:v>↓ Impacto imediato</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="str">
+        <x:v>Possibilidade de parcelamento da compra/reajuste do combustível em seis parcelas.</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="str"/>
+      <x:c r="G7" s="16" t="str">
+        <x:v>Distribui no tempo o impacto financeiro do combustível, reduzindo a necessidade de desembolso imediato. A medida atua sobre liquidez e previsibilidade de caixa; pode suavizar a pressão por repasses rápidos às tarifas, mas não elimina o custo do QAV.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="16" t="str">
+        <x:v>Redução do preço do QAV – junho</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>Jun/2026</x:v>
+      </x:c>
+      <x:c r="C8" s="16" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="str">
+        <x:v>↓ Custo</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="str">
+        <x:v>Petrobras reduziu o preço do QAV em 14,2%, equivalente a R$ 0,93/litro.</x:v>
+      </x:c>
+      <x:c r="F8" s="16" t="str"/>
+      <x:c r="G8" s="16" t="str">
+        <x:v>É um fator com efeito mais direto sobre a estrutura de custos das companhias: combustível mais barato reduz o custo operacional por voo. Isso pode favorecer manutenção ou expansão da oferta e reduzir pressão de alta nas tarifas. O repasse ao consumidor não é obrigatório nem imediato.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="16" t="str">
+        <x:v>Nova redução do QAV – julho</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>Jul/2026</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>Brasil</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>↓ Custo</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>Segunda queda consecutiva: -14,5%, equivalente a R$ 0,81/litro.</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="str"/>
+      <x:c r="G9" s="16" t="str">
+        <x:v>Reforça a redução do custo de combustível observada no mês anterior. Duas quedas consecutivas podem melhorar de forma mais persistente a estrutura de custos das aéreas, mas o preço final continua condicionado a demanda, concorrência, antecedência da compra e disponibilidade de assentos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="16" t="str">
         <x:v>Reajuste da tarifa do Salgado Filho</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B10" s="16" t="str">
         <x:v>Set/2025, vigente em 2026</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C10" s="16" t="str">
         <x:v>Porto Alegre</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="str">
+      <x:c r="D10" s="16" t="str">
         <x:v>↑ Custo para passageiro</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
+      <x:c r="E10" s="16" t="str">
         <x:v>Tarifa de embarque doméstico teve reajuste de 6,14%.</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="str"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="16"/>
-      <x:c r="B5" s="16"/>
-      <x:c r="C5" s="16"/>
-      <x:c r="D5" s="16"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="16"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="16"/>
-      <x:c r="B6" s="16"/>
-      <x:c r="C6" s="16"/>
-      <x:c r="D6" s="16"/>
-      <x:c r="E6" s="16"/>
-      <x:c r="F6" s="16"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="16"/>
-      <x:c r="B7" s="16"/>
-      <x:c r="C7" s="16"/>
-      <x:c r="D7" s="16"/>
-      <x:c r="E7" s="16"/>
-      <x:c r="F7" s="16"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="16"/>
-      <x:c r="B8" s="16"/>
-      <x:c r="C8" s="16"/>
-      <x:c r="D8" s="16"/>
-      <x:c r="E8" s="16"/>
-      <x:c r="F8" s="16"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="16"/>
-      <x:c r="B9" s="16"/>
-      <x:c r="C9" s="16"/>
-      <x:c r="D9" s="16"/>
-      <x:c r="E9" s="16"/>
-      <x:c r="F9" s="16"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="16"/>
-      <x:c r="B10" s="16"/>
-      <x:c r="C10" s="16"/>
-      <x:c r="D10" s="16"/>
-      <x:c r="E10" s="16"/>
-      <x:c r="F10" s="16"/>
+      <x:c r="F10" s="16" t="str"/>
+      <x:c r="G10" s="16" t="str">
+        <x:v>Aumenta o valor total desembolsado pelo passageiro ao viajar por Porto Alegre. Importante: a tarifa de embarque é uma tarifa aeroportuária e não compõe a Tarifa Aérea Média calculada pela ANAC. Assim, pode encarecer a viagem mesmo sem aparecer como aumento na série de tarifa média aérea.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="16"/>
-      <x:c r="B11" s="16"/>
-      <x:c r="C11" s="16"/>
-      <x:c r="D11" s="16"/>
-      <x:c r="E11" s="16"/>
-      <x:c r="F11" s="16"/>
+      <x:c r="A11" s="16" t="str">
+        <x:v>Reajuste da tarifa do Hercílio Luz</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>A partir de 31/08/2025</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>Santa Catarina</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>↑ Custo para passageiro</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>Tarifa de embarque doméstico teve reajuste de 5,97%.</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="str"/>
+      <x:c r="G11" s="16" t="str">
+        <x:v>Eleva o custo total para passageiros que embarcam por Florianópolis, um dos mercados emissores acompanhados. Como é tarifa aeroportuária, afeta o preço final da jornada, mas não entra no indicador de Tarifa Aérea Média da ANAC.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="16"/>
-      <x:c r="B12" s="16"/>
-      <x:c r="C12" s="16"/>
-      <x:c r="D12" s="16"/>
-      <x:c r="E12" s="16"/>
-      <x:c r="F12" s="16"/>
+      <x:c r="A12" s="16" t="str">
+        <x:v>Reajuste da tarifa do aeroporto de Guarulhos</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="str">
+        <x:v>Jul/2026</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="str">
+        <x:v>São Paulo</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="str">
+        <x:v>↑ Custo para passageiro</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="str">
+        <x:v>Tarifa de embarque doméstico teve reajuste de 6,27%.</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="str"/>
+      <x:c r="G12" s="16" t="str">
+        <x:v>Aumenta o custo total de uma viagem originada em Guarulhos. Pode reduzir marginalmente a atratividade de viajar de avião quando o passageiro compara o custo completo, mas esse reajuste não entra no valor da Tarifa Aérea Média ANAC.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="16"/>
-      <x:c r="B13" s="16"/>
-      <x:c r="C13" s="16"/>
-      <x:c r="D13" s="16"/>
-      <x:c r="E13" s="16"/>
-      <x:c r="F13" s="16"/>
+      <x:c r="A13" s="16" t="str">
+        <x:v>Reajuste da tarifa do aeroporto de Viracopos/Campinas</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>Jul/2026</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="str">
+        <x:v>São Paulo</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="str">
+        <x:v>↑ Custo para passageiro</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="str">
+        <x:v>Tarifa de embarque doméstico teve reajuste de 6,16%.</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="str"/>
+      <x:c r="G13" s="16" t="str">
+        <x:v>Eleva o custo final para viagens com origem em Viracopos/Campinas. É relevante para entender o custo total do deslocamento a partir de São Paulo, mas deve ser analisado separadamente da tarifa média da ANAC, porque a tarifa de embarque não compõe esse indicador.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="16"/>
-      <x:c r="B14" s="16"/>
-      <x:c r="C14" s="16"/>
-      <x:c r="D14" s="16"/>
-      <x:c r="E14" s="16"/>
-      <x:c r="F14" s="16"/>
+      <x:c r="A14" s="16" t="str">
+        <x:v>Rio de Janeiro – Galeão</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="str">
+        <x:v>Mai/2026</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="str">
+        <x:v>Rio de Janeiro</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="str">
+        <x:v>↑ Custo para passageiro</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="str">
+        <x:v>Tarifa de embarque doméstico teve reajuste de 6,28%.</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="str"/>
+      <x:c r="G14" s="16" t="str">
+        <x:v>O reajuste aumenta o valor total pago por passageiros que embarcam no Galeão. Para o monitor, isso é relevante porque RJ é um mercado emissor; porém, o aumento não aparece diretamente na Tarifa Aérea Média ANAC, já que a tarifa aeroportuária é cobrada separadamente.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="16"/>
-      <x:c r="B15" s="16"/>
-      <x:c r="C15" s="16"/>
-      <x:c r="D15" s="16"/>
-      <x:c r="E15" s="16"/>
-      <x:c r="F15" s="16"/>
+      <x:c r="A15" s="16" t="str">
+        <x:v>Reajuste da tarifa dos aeroportos de Belo Horizonte – Confins/Tancredo Neves</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>Mai/2026</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>Belo Horizonte</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>↑ Custo para passageiro</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>Tarifa de embarque doméstico teve reajuste de 4,74%.</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str"/>
+      <x:c r="G15" s="16" t="str">
+        <x:v>Aumenta o custo total de viajar a partir de Confins, origem utilizada no acompanhamento de Minas Gerais. Assim como nos demais aeroportos, esse valor é adicional ao serviço de transporte aéreo e não integra a Tarifa Aérea Média da ANAC.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="16"/>
@@ -30381,7 +30550,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff335cfd10e4301"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92755fdf65c444ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="R05cde3119ab64bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_TARIFAS_ANAC" sheetId="2" r:id="Rae58469db8494a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_GOOGLE_FLIGHTS" sheetId="3" r:id="R242b7e3558e94218"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCENTIVOS_MEDIDAS" sheetId="4" r:id="R35ea366599a74733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSARIO_METODOLOGIA" sheetId="5" r:id="R0394b19f902342a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="6" r:id="Rfc895460c20946c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="R7bf011cde4774d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_TARIFAS_ANAC" sheetId="2" r:id="Rf0947a8416a54dad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_GOOGLE_FLIGHTS" sheetId="3" r:id="Rd2a3a8937d8f45a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCENTIVOS_MEDIDAS" sheetId="4" r:id="R81de897402924a12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSARIO_METODOLOGIA" sheetId="5" r:id="R456f67a14bbe4e01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="6" r:id="R62e6e7d5c0254cdd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -208,13 +208,23 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="1">
+  <x:dxfs count="2">
     <x:dxf>
       <x:font>
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
         <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -14656,7 +14666,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf32fc2999cc47ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c3f4641eca54aee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24924,1102 +24934,2552 @@
       </x:c>
     </x:row>
     <x:row r="246">
-      <x:c r="A246" s="26"/>
-      <x:c r="B246" s="16"/>
-      <x:c r="C246" s="16"/>
-      <x:c r="D246" s="16"/>
-      <x:c r="E246" s="16"/>
+      <x:c r="A246" s="26" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="B246" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C246" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D246" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E246" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F246" s="26"/>
       <x:c r="G246" s="26"/>
-      <x:c r="H246" s="16"/>
+      <x:c r="H246" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I246" s="16"/>
-      <x:c r="J246" s="25"/>
-      <x:c r="K246" s="16"/>
-      <x:c r="L246" s="16"/>
+      <x:c r="J246" s="39" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K246" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L246" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M246" s="16"/>
-      <x:c r="N246" s="16"/>
-      <x:c r="O246" s="16"/>
-      <x:c r="P246" s="16"/>
+      <x:c r="N246" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O246" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P246" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="247">
-      <x:c r="A247" s="26"/>
-      <x:c r="B247" s="16"/>
-      <x:c r="C247" s="16"/>
-      <x:c r="D247" s="16"/>
-      <x:c r="E247" s="16"/>
+      <x:c r="A247" s="26" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="B247" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C247" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D247" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E247" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F247" s="26"/>
       <x:c r="G247" s="26"/>
-      <x:c r="H247" s="16"/>
+      <x:c r="H247" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I247" s="16"/>
-      <x:c r="J247" s="25"/>
-      <x:c r="K247" s="16"/>
-      <x:c r="L247" s="16"/>
+      <x:c r="J247" s="39"/>
+      <x:c r="K247" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L247" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M247" s="16"/>
-      <x:c r="N247" s="16"/>
-      <x:c r="O247" s="16"/>
-      <x:c r="P247" s="16"/>
+      <x:c r="N247" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O247" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P247" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="248">
-      <x:c r="A248" s="26"/>
-      <x:c r="B248" s="16"/>
-      <x:c r="C248" s="16"/>
-      <x:c r="D248" s="16"/>
-      <x:c r="E248" s="16"/>
+      <x:c r="A248" s="26" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="B248" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C248" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D248" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E248" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F248" s="26"/>
       <x:c r="G248" s="26"/>
-      <x:c r="H248" s="16"/>
+      <x:c r="H248" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I248" s="16"/>
-      <x:c r="J248" s="25"/>
-      <x:c r="K248" s="16"/>
-      <x:c r="L248" s="16"/>
+      <x:c r="J248" s="39" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K248" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L248" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M248" s="16"/>
-      <x:c r="N248" s="16"/>
-      <x:c r="O248" s="16"/>
-      <x:c r="P248" s="16"/>
+      <x:c r="N248" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O248" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P248" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="249">
-      <x:c r="A249" s="26"/>
-      <x:c r="B249" s="16"/>
-      <x:c r="C249" s="16"/>
-      <x:c r="D249" s="16"/>
-      <x:c r="E249" s="16"/>
+      <x:c r="A249" s="26" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="B249" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C249" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D249" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E249" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F249" s="26"/>
       <x:c r="G249" s="26"/>
-      <x:c r="H249" s="16"/>
+      <x:c r="H249" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I249" s="16"/>
-      <x:c r="J249" s="25"/>
-      <x:c r="K249" s="16"/>
-      <x:c r="L249" s="16"/>
+      <x:c r="J249" s="39" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K249" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L249" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M249" s="16"/>
-      <x:c r="N249" s="16"/>
-      <x:c r="O249" s="16"/>
-      <x:c r="P249" s="16"/>
+      <x:c r="N249" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O249" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P249" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="250">
-      <x:c r="A250" s="26"/>
-      <x:c r="B250" s="16"/>
-      <x:c r="C250" s="16"/>
-      <x:c r="D250" s="16"/>
-      <x:c r="E250" s="16"/>
+      <x:c r="A250" s="26" t="n">
+        <x:v>46185</x:v>
+      </x:c>
+      <x:c r="B250" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C250" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D250" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E250" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F250" s="26"/>
       <x:c r="G250" s="26"/>
-      <x:c r="H250" s="16"/>
+      <x:c r="H250" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I250" s="16"/>
-      <x:c r="J250" s="25"/>
-      <x:c r="K250" s="16"/>
-      <x:c r="L250" s="16"/>
+      <x:c r="J250" s="39" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K250" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L250" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M250" s="16"/>
-      <x:c r="N250" s="16"/>
-      <x:c r="O250" s="16"/>
-      <x:c r="P250" s="16"/>
+      <x:c r="N250" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O250" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P250" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="251">
-      <x:c r="A251" s="26"/>
-      <x:c r="B251" s="16"/>
-      <x:c r="C251" s="16"/>
-      <x:c r="D251" s="16"/>
-      <x:c r="E251" s="16"/>
+      <x:c r="A251" s="26" t="n">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="B251" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C251" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D251" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E251" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F251" s="26"/>
       <x:c r="G251" s="26"/>
-      <x:c r="H251" s="16"/>
+      <x:c r="H251" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I251" s="16"/>
-      <x:c r="J251" s="25"/>
-      <x:c r="K251" s="16"/>
-      <x:c r="L251" s="16"/>
+      <x:c r="J251" s="39" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="K251" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L251" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M251" s="16"/>
-      <x:c r="N251" s="16"/>
-      <x:c r="O251" s="16"/>
-      <x:c r="P251" s="16"/>
+      <x:c r="N251" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O251" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P251" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="252">
-      <x:c r="A252" s="26"/>
-      <x:c r="B252" s="16"/>
-      <x:c r="C252" s="16"/>
-      <x:c r="D252" s="16"/>
-      <x:c r="E252" s="16"/>
+      <x:c r="A252" s="26" t="n">
+        <x:v>46187</x:v>
+      </x:c>
+      <x:c r="B252" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C252" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D252" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E252" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F252" s="26"/>
       <x:c r="G252" s="26"/>
-      <x:c r="H252" s="16"/>
+      <x:c r="H252" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I252" s="16"/>
-      <x:c r="J252" s="25"/>
-      <x:c r="K252" s="16"/>
-      <x:c r="L252" s="16"/>
+      <x:c r="J252" s="39" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="K252" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L252" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M252" s="16"/>
-      <x:c r="N252" s="16"/>
-      <x:c r="O252" s="16"/>
-      <x:c r="P252" s="16"/>
+      <x:c r="N252" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O252" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P252" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
-      <x:c r="A253" s="26"/>
-      <x:c r="B253" s="16"/>
-      <x:c r="C253" s="16"/>
-      <x:c r="D253" s="16"/>
-      <x:c r="E253" s="16"/>
+      <x:c r="A253" s="26" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="B253" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C253" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D253" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E253" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F253" s="26"/>
       <x:c r="G253" s="26"/>
-      <x:c r="H253" s="16"/>
+      <x:c r="H253" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I253" s="16"/>
-      <x:c r="J253" s="25"/>
-      <x:c r="K253" s="16"/>
-      <x:c r="L253" s="16"/>
+      <x:c r="J253" s="39" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K253" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L253" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M253" s="16"/>
-      <x:c r="N253" s="16"/>
-      <x:c r="O253" s="16"/>
-      <x:c r="P253" s="16"/>
+      <x:c r="N253" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O253" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P253" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="254">
-      <x:c r="A254" s="26"/>
-      <x:c r="B254" s="16"/>
-      <x:c r="C254" s="16"/>
-      <x:c r="D254" s="16"/>
-      <x:c r="E254" s="16"/>
+      <x:c r="A254" s="26" t="n">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="B254" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C254" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D254" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E254" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F254" s="26"/>
       <x:c r="G254" s="26"/>
-      <x:c r="H254" s="16"/>
+      <x:c r="H254" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I254" s="16"/>
-      <x:c r="J254" s="25"/>
-      <x:c r="K254" s="16"/>
-      <x:c r="L254" s="16"/>
+      <x:c r="J254" s="39" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="K254" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L254" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M254" s="16"/>
-      <x:c r="N254" s="16"/>
-      <x:c r="O254" s="16"/>
-      <x:c r="P254" s="16"/>
+      <x:c r="N254" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O254" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P254" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="255">
-      <x:c r="A255" s="26"/>
-      <x:c r="B255" s="16"/>
-      <x:c r="C255" s="16"/>
-      <x:c r="D255" s="16"/>
-      <x:c r="E255" s="16"/>
+      <x:c r="A255" s="26" t="n">
+        <x:v>46190</x:v>
+      </x:c>
+      <x:c r="B255" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C255" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D255" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E255" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F255" s="26"/>
       <x:c r="G255" s="26"/>
-      <x:c r="H255" s="16"/>
+      <x:c r="H255" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I255" s="16"/>
-      <x:c r="J255" s="25"/>
-      <x:c r="K255" s="16"/>
-      <x:c r="L255" s="16"/>
+      <x:c r="J255" s="39" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="K255" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L255" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M255" s="16"/>
-      <x:c r="N255" s="16"/>
-      <x:c r="O255" s="16"/>
-      <x:c r="P255" s="16"/>
+      <x:c r="N255" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O255" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P255" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="256">
-      <x:c r="A256" s="26"/>
-      <x:c r="B256" s="16"/>
-      <x:c r="C256" s="16"/>
-      <x:c r="D256" s="16"/>
-      <x:c r="E256" s="16"/>
+      <x:c r="A256" s="26" t="n">
+        <x:v>46191</x:v>
+      </x:c>
+      <x:c r="B256" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C256" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D256" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E256" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F256" s="26"/>
       <x:c r="G256" s="26"/>
-      <x:c r="H256" s="16"/>
+      <x:c r="H256" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I256" s="16"/>
-      <x:c r="J256" s="25"/>
-      <x:c r="K256" s="16"/>
-      <x:c r="L256" s="16"/>
+      <x:c r="J256" s="39"/>
+      <x:c r="K256" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L256" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M256" s="16"/>
-      <x:c r="N256" s="16"/>
-      <x:c r="O256" s="16"/>
-      <x:c r="P256" s="16"/>
+      <x:c r="N256" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O256" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P256" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="257">
-      <x:c r="A257" s="26"/>
-      <x:c r="B257" s="16"/>
-      <x:c r="C257" s="16"/>
-      <x:c r="D257" s="16"/>
-      <x:c r="E257" s="16"/>
+      <x:c r="A257" s="26" t="n">
+        <x:v>46192</x:v>
+      </x:c>
+      <x:c r="B257" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C257" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D257" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E257" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F257" s="26"/>
       <x:c r="G257" s="26"/>
-      <x:c r="H257" s="16"/>
+      <x:c r="H257" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I257" s="16"/>
-      <x:c r="J257" s="25"/>
-      <x:c r="K257" s="16"/>
-      <x:c r="L257" s="16"/>
+      <x:c r="J257" s="39" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K257" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L257" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M257" s="16"/>
-      <x:c r="N257" s="16"/>
-      <x:c r="O257" s="16"/>
-      <x:c r="P257" s="16"/>
+      <x:c r="N257" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O257" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P257" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="258">
-      <x:c r="A258" s="26"/>
-      <x:c r="B258" s="16"/>
-      <x:c r="C258" s="16"/>
-      <x:c r="D258" s="16"/>
-      <x:c r="E258" s="16"/>
+      <x:c r="A258" s="26" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="B258" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C258" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D258" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E258" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F258" s="26"/>
       <x:c r="G258" s="26"/>
-      <x:c r="H258" s="16"/>
+      <x:c r="H258" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I258" s="16"/>
-      <x:c r="J258" s="25"/>
-      <x:c r="K258" s="16"/>
-      <x:c r="L258" s="16"/>
+      <x:c r="J258" s="39" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K258" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L258" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M258" s="16"/>
-      <x:c r="N258" s="16"/>
-      <x:c r="O258" s="16"/>
-      <x:c r="P258" s="16"/>
+      <x:c r="N258" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O258" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P258" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="259">
-      <x:c r="A259" s="26"/>
-      <x:c r="B259" s="16"/>
-      <x:c r="C259" s="16"/>
-      <x:c r="D259" s="16"/>
-      <x:c r="E259" s="16"/>
+      <x:c r="A259" s="26" t="n">
+        <x:v>46194</x:v>
+      </x:c>
+      <x:c r="B259" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C259" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D259" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E259" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F259" s="26"/>
       <x:c r="G259" s="26"/>
-      <x:c r="H259" s="16"/>
+      <x:c r="H259" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I259" s="16"/>
-      <x:c r="J259" s="25"/>
-      <x:c r="K259" s="16"/>
-      <x:c r="L259" s="16"/>
+      <x:c r="J259" s="39" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K259" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L259" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M259" s="16"/>
-      <x:c r="N259" s="16"/>
-      <x:c r="O259" s="16"/>
-      <x:c r="P259" s="16"/>
+      <x:c r="N259" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O259" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P259" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="260">
-      <x:c r="A260" s="26"/>
-      <x:c r="B260" s="16"/>
-      <x:c r="C260" s="16"/>
-      <x:c r="D260" s="16"/>
-      <x:c r="E260" s="16"/>
+      <x:c r="A260" s="26" t="n">
+        <x:v>46195</x:v>
+      </x:c>
+      <x:c r="B260" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C260" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D260" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E260" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F260" s="26"/>
       <x:c r="G260" s="26"/>
-      <x:c r="H260" s="16"/>
+      <x:c r="H260" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I260" s="16"/>
-      <x:c r="J260" s="25"/>
-      <x:c r="K260" s="16"/>
-      <x:c r="L260" s="16"/>
+      <x:c r="J260" s="39" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K260" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L260" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M260" s="16"/>
-      <x:c r="N260" s="16"/>
-      <x:c r="O260" s="16"/>
-      <x:c r="P260" s="16"/>
+      <x:c r="N260" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O260" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P260" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="261">
-      <x:c r="A261" s="26"/>
-      <x:c r="B261" s="16"/>
-      <x:c r="C261" s="16"/>
-      <x:c r="D261" s="16"/>
-      <x:c r="E261" s="16"/>
+      <x:c r="A261" s="26" t="n">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="B261" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C261" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D261" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E261" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F261" s="26"/>
       <x:c r="G261" s="26"/>
-      <x:c r="H261" s="16"/>
+      <x:c r="H261" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I261" s="16"/>
-      <x:c r="J261" s="25"/>
-      <x:c r="K261" s="16"/>
-      <x:c r="L261" s="16"/>
+      <x:c r="J261" s="39" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K261" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L261" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M261" s="16"/>
-      <x:c r="N261" s="16"/>
-      <x:c r="O261" s="16"/>
-      <x:c r="P261" s="16"/>
+      <x:c r="N261" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O261" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P261" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="262">
-      <x:c r="A262" s="26"/>
-      <x:c r="B262" s="16"/>
-      <x:c r="C262" s="16"/>
-      <x:c r="D262" s="16"/>
-      <x:c r="E262" s="16"/>
+      <x:c r="A262" s="26" t="n">
+        <x:v>46197</x:v>
+      </x:c>
+      <x:c r="B262" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C262" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D262" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E262" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F262" s="26"/>
       <x:c r="G262" s="26"/>
-      <x:c r="H262" s="16"/>
+      <x:c r="H262" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I262" s="16"/>
-      <x:c r="J262" s="25"/>
-      <x:c r="K262" s="16"/>
-      <x:c r="L262" s="16"/>
+      <x:c r="J262" s="39" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K262" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L262" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M262" s="16"/>
-      <x:c r="N262" s="16"/>
-      <x:c r="O262" s="16"/>
-      <x:c r="P262" s="16"/>
+      <x:c r="N262" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O262" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P262" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="263">
-      <x:c r="A263" s="26"/>
-      <x:c r="B263" s="16"/>
-      <x:c r="C263" s="16"/>
-      <x:c r="D263" s="16"/>
-      <x:c r="E263" s="16"/>
+      <x:c r="A263" s="26" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="B263" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C263" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D263" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E263" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F263" s="26"/>
       <x:c r="G263" s="26"/>
-      <x:c r="H263" s="16"/>
+      <x:c r="H263" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I263" s="16"/>
-      <x:c r="J263" s="25"/>
-      <x:c r="K263" s="16"/>
-      <x:c r="L263" s="16"/>
+      <x:c r="J263" s="39"/>
+      <x:c r="K263" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L263" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M263" s="16"/>
-      <x:c r="N263" s="16"/>
-      <x:c r="O263" s="16"/>
-      <x:c r="P263" s="16"/>
+      <x:c r="N263" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O263" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P263" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="264">
-      <x:c r="A264" s="26"/>
-      <x:c r="B264" s="16"/>
-      <x:c r="C264" s="16"/>
-      <x:c r="D264" s="16"/>
-      <x:c r="E264" s="16"/>
+      <x:c r="A264" s="26" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B264" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C264" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D264" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E264" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F264" s="26"/>
       <x:c r="G264" s="26"/>
-      <x:c r="H264" s="16"/>
+      <x:c r="H264" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I264" s="16"/>
-      <x:c r="J264" s="25"/>
-      <x:c r="K264" s="16"/>
-      <x:c r="L264" s="16"/>
+      <x:c r="J264" s="39" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K264" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L264" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M264" s="16"/>
-      <x:c r="N264" s="16"/>
-      <x:c r="O264" s="16"/>
-      <x:c r="P264" s="16"/>
+      <x:c r="N264" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O264" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P264" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="265">
-      <x:c r="A265" s="26"/>
-      <x:c r="B265" s="16"/>
-      <x:c r="C265" s="16"/>
-      <x:c r="D265" s="16"/>
-      <x:c r="E265" s="16"/>
+      <x:c r="A265" s="26" t="n">
+        <x:v>46200</x:v>
+      </x:c>
+      <x:c r="B265" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C265" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D265" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E265" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F265" s="26"/>
       <x:c r="G265" s="26"/>
-      <x:c r="H265" s="16"/>
+      <x:c r="H265" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I265" s="16"/>
-      <x:c r="J265" s="25"/>
-      <x:c r="K265" s="16"/>
-      <x:c r="L265" s="16"/>
+      <x:c r="J265" s="39" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="K265" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L265" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M265" s="16"/>
-      <x:c r="N265" s="16"/>
-      <x:c r="O265" s="16"/>
-      <x:c r="P265" s="16"/>
+      <x:c r="N265" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O265" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P265" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="266">
-      <x:c r="A266" s="26"/>
-      <x:c r="B266" s="16"/>
-      <x:c r="C266" s="16"/>
-      <x:c r="D266" s="16"/>
-      <x:c r="E266" s="16"/>
+      <x:c r="A266" s="26" t="n">
+        <x:v>46201</x:v>
+      </x:c>
+      <x:c r="B266" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C266" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D266" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E266" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F266" s="26"/>
       <x:c r="G266" s="26"/>
-      <x:c r="H266" s="16"/>
+      <x:c r="H266" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I266" s="16"/>
-      <x:c r="J266" s="25"/>
-      <x:c r="K266" s="16"/>
-      <x:c r="L266" s="16"/>
+      <x:c r="J266" s="39" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="K266" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L266" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M266" s="16"/>
-      <x:c r="N266" s="16"/>
-      <x:c r="O266" s="16"/>
-      <x:c r="P266" s="16"/>
+      <x:c r="N266" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O266" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P266" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="267">
-      <x:c r="A267" s="26"/>
-      <x:c r="B267" s="16"/>
-      <x:c r="C267" s="16"/>
-      <x:c r="D267" s="16"/>
-      <x:c r="E267" s="16"/>
+      <x:c r="A267" s="26" t="n">
+        <x:v>46202</x:v>
+      </x:c>
+      <x:c r="B267" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C267" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D267" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E267" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F267" s="26"/>
       <x:c r="G267" s="26"/>
-      <x:c r="H267" s="16"/>
+      <x:c r="H267" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I267" s="16"/>
-      <x:c r="J267" s="25"/>
-      <x:c r="K267" s="16"/>
-      <x:c r="L267" s="16"/>
+      <x:c r="J267" s="39" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="K267" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L267" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M267" s="16"/>
-      <x:c r="N267" s="16"/>
-      <x:c r="O267" s="16"/>
-      <x:c r="P267" s="16"/>
+      <x:c r="N267" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O267" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P267" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="268">
-      <x:c r="A268" s="26"/>
-      <x:c r="B268" s="16"/>
-      <x:c r="C268" s="16"/>
-      <x:c r="D268" s="16"/>
-      <x:c r="E268" s="16"/>
+      <x:c r="A268" s="26" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B268" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C268" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D268" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E268" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F268" s="26"/>
       <x:c r="G268" s="26"/>
-      <x:c r="H268" s="16"/>
+      <x:c r="H268" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I268" s="16"/>
-      <x:c r="J268" s="25"/>
-      <x:c r="K268" s="16"/>
-      <x:c r="L268" s="16"/>
+      <x:c r="J268" s="39" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K268" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L268" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M268" s="16"/>
-      <x:c r="N268" s="16"/>
-      <x:c r="O268" s="16"/>
-      <x:c r="P268" s="16"/>
+      <x:c r="N268" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O268" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P268" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="269">
-      <x:c r="A269" s="26"/>
-      <x:c r="B269" s="16"/>
-      <x:c r="C269" s="16"/>
-      <x:c r="D269" s="16"/>
-      <x:c r="E269" s="16"/>
+      <x:c r="A269" s="26" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B269" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C269" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D269" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E269" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F269" s="26"/>
       <x:c r="G269" s="26"/>
-      <x:c r="H269" s="16"/>
+      <x:c r="H269" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I269" s="16"/>
-      <x:c r="J269" s="25"/>
-      <x:c r="K269" s="16"/>
-      <x:c r="L269" s="16"/>
+      <x:c r="J269" s="39" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K269" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L269" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M269" s="16"/>
-      <x:c r="N269" s="16"/>
-      <x:c r="O269" s="16"/>
-      <x:c r="P269" s="16"/>
+      <x:c r="N269" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O269" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P269" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="270">
-      <x:c r="A270" s="26"/>
-      <x:c r="B270" s="16"/>
-      <x:c r="C270" s="16"/>
-      <x:c r="D270" s="16"/>
-      <x:c r="E270" s="16"/>
+      <x:c r="A270" s="26" t="n">
+        <x:v>46205</x:v>
+      </x:c>
+      <x:c r="B270" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C270" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D270" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E270" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F270" s="26"/>
       <x:c r="G270" s="26"/>
-      <x:c r="H270" s="16"/>
+      <x:c r="H270" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I270" s="16"/>
-      <x:c r="J270" s="25"/>
-      <x:c r="K270" s="16"/>
-      <x:c r="L270" s="16"/>
+      <x:c r="J270" s="39" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K270" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L270" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M270" s="16"/>
-      <x:c r="N270" s="16"/>
-      <x:c r="O270" s="16"/>
-      <x:c r="P270" s="16"/>
+      <x:c r="N270" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O270" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P270" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="271">
-      <x:c r="A271" s="26"/>
-      <x:c r="B271" s="16"/>
-      <x:c r="C271" s="16"/>
-      <x:c r="D271" s="16"/>
-      <x:c r="E271" s="16"/>
+      <x:c r="A271" s="26" t="n">
+        <x:v>46206</x:v>
+      </x:c>
+      <x:c r="B271" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C271" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D271" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E271" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F271" s="26"/>
       <x:c r="G271" s="26"/>
-      <x:c r="H271" s="16"/>
+      <x:c r="H271" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I271" s="16"/>
-      <x:c r="J271" s="25"/>
-      <x:c r="K271" s="16"/>
-      <x:c r="L271" s="16"/>
+      <x:c r="J271" s="39" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="K271" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L271" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M271" s="16"/>
-      <x:c r="N271" s="16"/>
-      <x:c r="O271" s="16"/>
-      <x:c r="P271" s="16"/>
+      <x:c r="N271" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O271" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P271" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="272">
-      <x:c r="A272" s="26"/>
-      <x:c r="B272" s="16"/>
-      <x:c r="C272" s="16"/>
-      <x:c r="D272" s="16"/>
-      <x:c r="E272" s="16"/>
+      <x:c r="A272" s="26" t="n">
+        <x:v>46207</x:v>
+      </x:c>
+      <x:c r="B272" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C272" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D272" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E272" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F272" s="26"/>
       <x:c r="G272" s="26"/>
-      <x:c r="H272" s="16"/>
+      <x:c r="H272" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I272" s="16"/>
-      <x:c r="J272" s="25"/>
-      <x:c r="K272" s="16"/>
-      <x:c r="L272" s="16"/>
+      <x:c r="J272" s="39" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K272" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L272" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M272" s="16"/>
-      <x:c r="N272" s="16"/>
-      <x:c r="O272" s="16"/>
-      <x:c r="P272" s="16"/>
+      <x:c r="N272" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O272" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P272" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="273">
-      <x:c r="A273" s="26"/>
-      <x:c r="B273" s="16"/>
-      <x:c r="C273" s="16"/>
-      <x:c r="D273" s="16"/>
-      <x:c r="E273" s="16"/>
+      <x:c r="A273" s="26" t="n">
+        <x:v>46208</x:v>
+      </x:c>
+      <x:c r="B273" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C273" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D273" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E273" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F273" s="26"/>
       <x:c r="G273" s="26"/>
-      <x:c r="H273" s="16"/>
+      <x:c r="H273" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I273" s="16"/>
-      <x:c r="J273" s="25"/>
-      <x:c r="K273" s="16"/>
-      <x:c r="L273" s="16"/>
+      <x:c r="J273" s="39" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K273" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L273" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M273" s="16"/>
-      <x:c r="N273" s="16"/>
-      <x:c r="O273" s="16"/>
-      <x:c r="P273" s="16"/>
+      <x:c r="N273" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O273" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P273" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="274">
-      <x:c r="A274" s="26"/>
-      <x:c r="B274" s="16"/>
-      <x:c r="C274" s="16"/>
-      <x:c r="D274" s="16"/>
-      <x:c r="E274" s="16"/>
+      <x:c r="A274" s="26" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="B274" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C274" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D274" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E274" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F274" s="26"/>
       <x:c r="G274" s="26"/>
-      <x:c r="H274" s="16"/>
+      <x:c r="H274" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I274" s="16"/>
-      <x:c r="J274" s="25"/>
-      <x:c r="K274" s="16"/>
-      <x:c r="L274" s="16"/>
+      <x:c r="J274" s="39" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K274" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L274" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M274" s="16"/>
-      <x:c r="N274" s="16"/>
-      <x:c r="O274" s="16"/>
-      <x:c r="P274" s="16"/>
+      <x:c r="N274" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O274" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P274" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="275">
-      <x:c r="A275" s="26"/>
-      <x:c r="B275" s="16"/>
-      <x:c r="C275" s="16"/>
-      <x:c r="D275" s="16"/>
-      <x:c r="E275" s="16"/>
+      <x:c r="A275" s="26" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B275" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C275" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D275" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E275" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F275" s="26"/>
       <x:c r="G275" s="26"/>
-      <x:c r="H275" s="16"/>
+      <x:c r="H275" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I275" s="16"/>
-      <x:c r="J275" s="25"/>
-      <x:c r="K275" s="16"/>
-      <x:c r="L275" s="16"/>
+      <x:c r="J275" s="39" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K275" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L275" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M275" s="16"/>
-      <x:c r="N275" s="16"/>
-      <x:c r="O275" s="16"/>
-      <x:c r="P275" s="16"/>
+      <x:c r="N275" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O275" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P275" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="276">
-      <x:c r="A276" s="26"/>
-      <x:c r="B276" s="16"/>
-      <x:c r="C276" s="16"/>
-      <x:c r="D276" s="16"/>
-      <x:c r="E276" s="16"/>
+      <x:c r="A276" s="26" t="n">
+        <x:v>46211</x:v>
+      </x:c>
+      <x:c r="B276" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C276" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D276" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E276" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F276" s="26"/>
       <x:c r="G276" s="26"/>
-      <x:c r="H276" s="16"/>
+      <x:c r="H276" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I276" s="16"/>
-      <x:c r="J276" s="25"/>
-      <x:c r="K276" s="16"/>
-      <x:c r="L276" s="16"/>
+      <x:c r="J276" s="39" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K276" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L276" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M276" s="16"/>
-      <x:c r="N276" s="16"/>
-      <x:c r="O276" s="16"/>
-      <x:c r="P276" s="16"/>
+      <x:c r="N276" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O276" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P276" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="277">
-      <x:c r="A277" s="26"/>
-      <x:c r="B277" s="16"/>
-      <x:c r="C277" s="16"/>
-      <x:c r="D277" s="16"/>
-      <x:c r="E277" s="16"/>
+      <x:c r="A277" s="26" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="B277" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C277" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D277" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E277" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F277" s="26"/>
       <x:c r="G277" s="26"/>
-      <x:c r="H277" s="16"/>
+      <x:c r="H277" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I277" s="16"/>
-      <x:c r="J277" s="25"/>
-      <x:c r="K277" s="16"/>
-      <x:c r="L277" s="16"/>
+      <x:c r="J277" s="39" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K277" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L277" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M277" s="16"/>
-      <x:c r="N277" s="16"/>
-      <x:c r="O277" s="16"/>
-      <x:c r="P277" s="16"/>
+      <x:c r="N277" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O277" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P277" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="278">
-      <x:c r="A278" s="26"/>
-      <x:c r="B278" s="16"/>
-      <x:c r="C278" s="16"/>
-      <x:c r="D278" s="16"/>
-      <x:c r="E278" s="16"/>
+      <x:c r="A278" s="26" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B278" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C278" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D278" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E278" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F278" s="26"/>
       <x:c r="G278" s="26"/>
-      <x:c r="H278" s="16"/>
+      <x:c r="H278" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I278" s="16"/>
-      <x:c r="J278" s="25"/>
-      <x:c r="K278" s="16"/>
-      <x:c r="L278" s="16"/>
+      <x:c r="J278" s="39" t="n">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="K278" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L278" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M278" s="16"/>
-      <x:c r="N278" s="16"/>
-      <x:c r="O278" s="16"/>
-      <x:c r="P278" s="16"/>
+      <x:c r="N278" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O278" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P278" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="279">
-      <x:c r="A279" s="26"/>
-      <x:c r="B279" s="16"/>
-      <x:c r="C279" s="16"/>
-      <x:c r="D279" s="16"/>
-      <x:c r="E279" s="16"/>
+      <x:c r="A279" s="26" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B279" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C279" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D279" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E279" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F279" s="26"/>
       <x:c r="G279" s="26"/>
-      <x:c r="H279" s="16"/>
+      <x:c r="H279" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I279" s="16"/>
-      <x:c r="J279" s="25"/>
-      <x:c r="K279" s="16"/>
-      <x:c r="L279" s="16"/>
+      <x:c r="J279" s="39" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K279" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L279" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M279" s="16"/>
-      <x:c r="N279" s="16"/>
-      <x:c r="O279" s="16"/>
-      <x:c r="P279" s="16"/>
+      <x:c r="N279" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O279" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P279" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="280">
-      <x:c r="A280" s="26"/>
-      <x:c r="B280" s="16"/>
-      <x:c r="C280" s="16"/>
-      <x:c r="D280" s="16"/>
-      <x:c r="E280" s="16"/>
+      <x:c r="A280" s="26" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B280" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C280" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D280" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E280" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F280" s="26"/>
       <x:c r="G280" s="26"/>
-      <x:c r="H280" s="16"/>
+      <x:c r="H280" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I280" s="16"/>
-      <x:c r="J280" s="25"/>
-      <x:c r="K280" s="16"/>
-      <x:c r="L280" s="16"/>
+      <x:c r="J280" s="39" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K280" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L280" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M280" s="16"/>
-      <x:c r="N280" s="16"/>
-      <x:c r="O280" s="16"/>
-      <x:c r="P280" s="16"/>
+      <x:c r="N280" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O280" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P280" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="281">
-      <x:c r="A281" s="26"/>
-      <x:c r="B281" s="16"/>
-      <x:c r="C281" s="16"/>
-      <x:c r="D281" s="16"/>
-      <x:c r="E281" s="16"/>
+      <x:c r="A281" s="26" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B281" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C281" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D281" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E281" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F281" s="26"/>
       <x:c r="G281" s="26"/>
-      <x:c r="H281" s="16"/>
+      <x:c r="H281" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I281" s="16"/>
-      <x:c r="J281" s="25"/>
-      <x:c r="K281" s="16"/>
-      <x:c r="L281" s="16"/>
+      <x:c r="J281" s="39" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K281" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L281" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M281" s="16"/>
-      <x:c r="N281" s="16"/>
-      <x:c r="O281" s="16"/>
-      <x:c r="P281" s="16"/>
+      <x:c r="N281" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O281" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P281" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="282">
-      <x:c r="A282" s="26"/>
-      <x:c r="B282" s="16"/>
-      <x:c r="C282" s="16"/>
-      <x:c r="D282" s="16"/>
-      <x:c r="E282" s="16"/>
+      <x:c r="A282" s="26" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B282" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C282" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D282" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E282" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F282" s="26"/>
       <x:c r="G282" s="26"/>
-      <x:c r="H282" s="16"/>
+      <x:c r="H282" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I282" s="16"/>
-      <x:c r="J282" s="25"/>
-      <x:c r="K282" s="16"/>
-      <x:c r="L282" s="16"/>
+      <x:c r="J282" s="39"/>
+      <x:c r="K282" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L282" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M282" s="16"/>
-      <x:c r="N282" s="16"/>
-      <x:c r="O282" s="16"/>
-      <x:c r="P282" s="16"/>
+      <x:c r="N282" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O282" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P282" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="283">
-      <x:c r="A283" s="26"/>
-      <x:c r="B283" s="16"/>
-      <x:c r="C283" s="16"/>
-      <x:c r="D283" s="16"/>
-      <x:c r="E283" s="16"/>
+      <x:c r="A283" s="26" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B283" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C283" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D283" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E283" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F283" s="26"/>
       <x:c r="G283" s="26"/>
-      <x:c r="H283" s="16"/>
+      <x:c r="H283" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I283" s="16"/>
-      <x:c r="J283" s="25"/>
-      <x:c r="K283" s="16"/>
-      <x:c r="L283" s="16"/>
+      <x:c r="J283" s="39" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="K283" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L283" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M283" s="16"/>
-      <x:c r="N283" s="16"/>
-      <x:c r="O283" s="16"/>
-      <x:c r="P283" s="16"/>
+      <x:c r="N283" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O283" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P283" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="284">
-      <x:c r="A284" s="26"/>
-      <x:c r="B284" s="16"/>
-      <x:c r="C284" s="16"/>
-      <x:c r="D284" s="16"/>
-      <x:c r="E284" s="16"/>
+      <x:c r="A284" s="26" t="n">
+        <x:v>46219</x:v>
+      </x:c>
+      <x:c r="B284" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C284" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D284" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E284" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F284" s="26"/>
       <x:c r="G284" s="26"/>
-      <x:c r="H284" s="16"/>
+      <x:c r="H284" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I284" s="16"/>
-      <x:c r="J284" s="25"/>
-      <x:c r="K284" s="16"/>
-      <x:c r="L284" s="16"/>
+      <x:c r="J284" s="39" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="K284" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L284" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M284" s="16"/>
-      <x:c r="N284" s="16"/>
-      <x:c r="O284" s="16"/>
-      <x:c r="P284" s="16"/>
+      <x:c r="N284" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O284" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P284" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="285">
-      <x:c r="A285" s="26"/>
-      <x:c r="B285" s="16"/>
-      <x:c r="C285" s="16"/>
-      <x:c r="D285" s="16"/>
-      <x:c r="E285" s="16"/>
+      <x:c r="A285" s="26" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B285" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C285" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D285" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E285" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F285" s="26"/>
       <x:c r="G285" s="26"/>
-      <x:c r="H285" s="16"/>
+      <x:c r="H285" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I285" s="16"/>
-      <x:c r="J285" s="25"/>
-      <x:c r="K285" s="16"/>
-      <x:c r="L285" s="16"/>
+      <x:c r="J285" s="39" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="K285" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L285" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M285" s="16"/>
-      <x:c r="N285" s="16"/>
-      <x:c r="O285" s="16"/>
-      <x:c r="P285" s="16"/>
+      <x:c r="N285" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O285" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P285" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="286">
-      <x:c r="A286" s="26"/>
-      <x:c r="B286" s="16"/>
-      <x:c r="C286" s="16"/>
-      <x:c r="D286" s="16"/>
-      <x:c r="E286" s="16"/>
+      <x:c r="A286" s="26" t="n">
+        <x:v>46221</x:v>
+      </x:c>
+      <x:c r="B286" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C286" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D286" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E286" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F286" s="26"/>
       <x:c r="G286" s="26"/>
-      <x:c r="H286" s="16"/>
+      <x:c r="H286" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I286" s="16"/>
-      <x:c r="J286" s="25"/>
-      <x:c r="K286" s="16"/>
-      <x:c r="L286" s="16"/>
+      <x:c r="J286" s="39" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K286" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L286" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M286" s="16"/>
-      <x:c r="N286" s="16"/>
-      <x:c r="O286" s="16"/>
-      <x:c r="P286" s="16"/>
+      <x:c r="N286" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O286" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P286" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="287">
-      <x:c r="A287" s="26"/>
-      <x:c r="B287" s="16"/>
-      <x:c r="C287" s="16"/>
-      <x:c r="D287" s="16"/>
-      <x:c r="E287" s="16"/>
+      <x:c r="A287" s="26" t="n">
+        <x:v>46222</x:v>
+      </x:c>
+      <x:c r="B287" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C287" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D287" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E287" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F287" s="26"/>
       <x:c r="G287" s="26"/>
-      <x:c r="H287" s="16"/>
+      <x:c r="H287" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I287" s="16"/>
-      <x:c r="J287" s="25"/>
-      <x:c r="K287" s="16"/>
-      <x:c r="L287" s="16"/>
+      <x:c r="J287" s="39"/>
+      <x:c r="K287" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L287" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M287" s="16"/>
-      <x:c r="N287" s="16"/>
-      <x:c r="O287" s="16"/>
-      <x:c r="P287" s="16"/>
+      <x:c r="N287" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O287" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P287" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="288">
-      <x:c r="A288" s="26"/>
-      <x:c r="B288" s="16"/>
-      <x:c r="C288" s="16"/>
-      <x:c r="D288" s="16"/>
-      <x:c r="E288" s="16"/>
+      <x:c r="A288" s="26" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B288" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C288" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D288" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E288" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F288" s="26"/>
       <x:c r="G288" s="26"/>
-      <x:c r="H288" s="16"/>
+      <x:c r="H288" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I288" s="16"/>
-      <x:c r="J288" s="25"/>
-      <x:c r="K288" s="16"/>
-      <x:c r="L288" s="16"/>
+      <x:c r="J288" s="39" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="K288" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L288" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M288" s="16"/>
-      <x:c r="N288" s="16"/>
-      <x:c r="O288" s="16"/>
-      <x:c r="P288" s="16"/>
+      <x:c r="N288" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O288" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P288" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="289">
-      <x:c r="A289" s="26"/>
-      <x:c r="B289" s="16"/>
-      <x:c r="C289" s="16"/>
-      <x:c r="D289" s="16"/>
-      <x:c r="E289" s="16"/>
+      <x:c r="A289" s="26" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="B289" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C289" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D289" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E289" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F289" s="26"/>
       <x:c r="G289" s="26"/>
-      <x:c r="H289" s="16"/>
+      <x:c r="H289" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I289" s="16"/>
-      <x:c r="J289" s="25"/>
-      <x:c r="K289" s="16"/>
-      <x:c r="L289" s="16"/>
+      <x:c r="J289" s="39" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K289" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L289" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M289" s="16"/>
-      <x:c r="N289" s="16"/>
-      <x:c r="O289" s="16"/>
-      <x:c r="P289" s="16"/>
+      <x:c r="N289" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O289" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P289" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="290">
-      <x:c r="A290" s="26"/>
-      <x:c r="B290" s="16"/>
-      <x:c r="C290" s="16"/>
-      <x:c r="D290" s="16"/>
-      <x:c r="E290" s="16"/>
+      <x:c r="A290" s="26" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="B290" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C290" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D290" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E290" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F290" s="26"/>
       <x:c r="G290" s="26"/>
-      <x:c r="H290" s="16"/>
+      <x:c r="H290" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I290" s="16"/>
-      <x:c r="J290" s="25"/>
-      <x:c r="K290" s="16"/>
-      <x:c r="L290" s="16"/>
+      <x:c r="J290" s="39" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K290" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L290" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M290" s="16"/>
-      <x:c r="N290" s="16"/>
-      <x:c r="O290" s="16"/>
-      <x:c r="P290" s="16"/>
+      <x:c r="N290" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O290" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P290" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="291">
-      <x:c r="A291" s="26"/>
-      <x:c r="B291" s="16"/>
-      <x:c r="C291" s="16"/>
-      <x:c r="D291" s="16"/>
-      <x:c r="E291" s="16"/>
+      <x:c r="A291" s="26" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="B291" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C291" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D291" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E291" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F291" s="26"/>
       <x:c r="G291" s="26"/>
-      <x:c r="H291" s="16"/>
+      <x:c r="H291" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I291" s="16"/>
-      <x:c r="J291" s="25"/>
-      <x:c r="K291" s="16"/>
-      <x:c r="L291" s="16"/>
+      <x:c r="J291" s="39" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K291" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L291" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M291" s="16"/>
-      <x:c r="N291" s="16"/>
-      <x:c r="O291" s="16"/>
-      <x:c r="P291" s="16"/>
+      <x:c r="N291" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O291" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P291" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="292">
-      <x:c r="A292" s="26"/>
-      <x:c r="B292" s="16"/>
-      <x:c r="C292" s="16"/>
-      <x:c r="D292" s="16"/>
-      <x:c r="E292" s="16"/>
+      <x:c r="A292" s="26" t="n">
+        <x:v>46227</x:v>
+      </x:c>
+      <x:c r="B292" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C292" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D292" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E292" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F292" s="26"/>
       <x:c r="G292" s="26"/>
-      <x:c r="H292" s="16"/>
+      <x:c r="H292" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I292" s="16"/>
-      <x:c r="J292" s="25"/>
-      <x:c r="K292" s="16"/>
-      <x:c r="L292" s="16"/>
+      <x:c r="J292" s="39" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K292" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L292" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M292" s="16"/>
-      <x:c r="N292" s="16"/>
-      <x:c r="O292" s="16"/>
-      <x:c r="P292" s="16"/>
+      <x:c r="N292" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O292" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P292" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="293">
-      <x:c r="A293" s="26"/>
-      <x:c r="B293" s="16"/>
-      <x:c r="C293" s="16"/>
-      <x:c r="D293" s="16"/>
-      <x:c r="E293" s="16"/>
+      <x:c r="A293" s="26" t="n">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="B293" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C293" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D293" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E293" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F293" s="26"/>
       <x:c r="G293" s="26"/>
-      <x:c r="H293" s="16"/>
+      <x:c r="H293" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I293" s="16"/>
-      <x:c r="J293" s="25"/>
-      <x:c r="K293" s="16"/>
-      <x:c r="L293" s="16"/>
+      <x:c r="J293" s="39" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K293" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L293" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M293" s="16"/>
-      <x:c r="N293" s="16"/>
-      <x:c r="O293" s="16"/>
-      <x:c r="P293" s="16"/>
+      <x:c r="N293" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O293" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P293" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="294">
-      <x:c r="A294" s="26"/>
-      <x:c r="B294" s="16"/>
-      <x:c r="C294" s="16"/>
-      <x:c r="D294" s="16"/>
-      <x:c r="E294" s="16"/>
+      <x:c r="A294" s="26" t="n">
+        <x:v>46229</x:v>
+      </x:c>
+      <x:c r="B294" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C294" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D294" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E294" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F294" s="26"/>
       <x:c r="G294" s="26"/>
-      <x:c r="H294" s="16"/>
+      <x:c r="H294" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I294" s="16"/>
-      <x:c r="J294" s="25"/>
-      <x:c r="K294" s="16"/>
-      <x:c r="L294" s="16"/>
+      <x:c r="J294" s="39" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K294" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L294" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M294" s="16"/>
-      <x:c r="N294" s="16"/>
-      <x:c r="O294" s="16"/>
-      <x:c r="P294" s="16"/>
+      <x:c r="N294" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O294" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P294" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="295">
-      <x:c r="A295" s="26"/>
-      <x:c r="B295" s="16"/>
-      <x:c r="C295" s="16"/>
-      <x:c r="D295" s="16"/>
-      <x:c r="E295" s="16"/>
+      <x:c r="A295" s="26" t="n">
+        <x:v>46230</x:v>
+      </x:c>
+      <x:c r="B295" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C295" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D295" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E295" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F295" s="26"/>
       <x:c r="G295" s="26"/>
-      <x:c r="H295" s="16"/>
+      <x:c r="H295" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I295" s="16"/>
-      <x:c r="J295" s="25"/>
-      <x:c r="K295" s="16"/>
-      <x:c r="L295" s="16"/>
+      <x:c r="J295" s="39" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K295" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L295" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M295" s="16"/>
-      <x:c r="N295" s="16"/>
-      <x:c r="O295" s="16"/>
-      <x:c r="P295" s="16"/>
+      <x:c r="N295" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O295" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P295" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="296">
-      <x:c r="A296" s="26"/>
-      <x:c r="B296" s="16"/>
-      <x:c r="C296" s="16"/>
-      <x:c r="D296" s="16"/>
-      <x:c r="E296" s="16"/>
+      <x:c r="A296" s="26" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="B296" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C296" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D296" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E296" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F296" s="26"/>
       <x:c r="G296" s="26"/>
-      <x:c r="H296" s="16"/>
+      <x:c r="H296" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I296" s="16"/>
-      <x:c r="J296" s="25"/>
-      <x:c r="K296" s="16"/>
-      <x:c r="L296" s="16"/>
+      <x:c r="J296" s="39" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="K296" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L296" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M296" s="16"/>
-      <x:c r="N296" s="16"/>
-      <x:c r="O296" s="16"/>
-      <x:c r="P296" s="16"/>
+      <x:c r="N296" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O296" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P296" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="297">
-      <x:c r="A297" s="26"/>
-      <x:c r="B297" s="16"/>
-      <x:c r="C297" s="16"/>
-      <x:c r="D297" s="16"/>
-      <x:c r="E297" s="16"/>
+      <x:c r="A297" s="26" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="B297" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C297" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D297" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E297" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F297" s="26"/>
       <x:c r="G297" s="26"/>
-      <x:c r="H297" s="16"/>
+      <x:c r="H297" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I297" s="16"/>
-      <x:c r="J297" s="25"/>
-      <x:c r="K297" s="16"/>
-      <x:c r="L297" s="16"/>
+      <x:c r="J297" s="39" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K297" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L297" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M297" s="16"/>
-      <x:c r="N297" s="16"/>
-      <x:c r="O297" s="16"/>
-      <x:c r="P297" s="16"/>
+      <x:c r="N297" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O297" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P297" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="298">
-      <x:c r="A298" s="26"/>
-      <x:c r="B298" s="16"/>
-      <x:c r="C298" s="16"/>
-      <x:c r="D298" s="16"/>
-      <x:c r="E298" s="16"/>
+      <x:c r="A298" s="26" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="B298" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C298" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D298" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E298" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F298" s="26"/>
       <x:c r="G298" s="26"/>
-      <x:c r="H298" s="16"/>
+      <x:c r="H298" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I298" s="16"/>
-      <x:c r="J298" s="25"/>
-      <x:c r="K298" s="16"/>
-      <x:c r="L298" s="16"/>
+      <x:c r="J298" s="39" t="n">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="K298" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L298" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M298" s="16"/>
-      <x:c r="N298" s="16"/>
-      <x:c r="O298" s="16"/>
-      <x:c r="P298" s="16"/>
+      <x:c r="N298" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O298" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P298" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="299">
-      <x:c r="A299" s="26"/>
-      <x:c r="B299" s="16"/>
-      <x:c r="C299" s="16"/>
-      <x:c r="D299" s="16"/>
-      <x:c r="E299" s="16"/>
+      <x:c r="A299" s="26" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B299" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C299" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D299" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E299" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F299" s="26"/>
       <x:c r="G299" s="26"/>
-      <x:c r="H299" s="16"/>
+      <x:c r="H299" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I299" s="16"/>
-      <x:c r="J299" s="25"/>
-      <x:c r="K299" s="16"/>
-      <x:c r="L299" s="16"/>
+      <x:c r="J299" s="39"/>
+      <x:c r="K299" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L299" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M299" s="16"/>
-      <x:c r="N299" s="16"/>
-      <x:c r="O299" s="16"/>
-      <x:c r="P299" s="16"/>
+      <x:c r="N299" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O299" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P299" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="300">
-      <x:c r="A300" s="26"/>
-      <x:c r="B300" s="16"/>
-      <x:c r="C300" s="16"/>
-      <x:c r="D300" s="16"/>
-      <x:c r="E300" s="16"/>
+      <x:c r="A300" s="26" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B300" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C300" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D300" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E300" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F300" s="26"/>
       <x:c r="G300" s="26"/>
-      <x:c r="H300" s="16"/>
+      <x:c r="H300" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I300" s="16"/>
-      <x:c r="J300" s="25"/>
-      <x:c r="K300" s="16"/>
-      <x:c r="L300" s="16"/>
+      <x:c r="J300" s="39" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K300" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L300" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M300" s="16"/>
-      <x:c r="N300" s="16"/>
-      <x:c r="O300" s="16"/>
-      <x:c r="P300" s="16"/>
+      <x:c r="N300" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O300" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P300" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="301">
-      <x:c r="A301" s="26"/>
-      <x:c r="B301" s="16"/>
-      <x:c r="C301" s="16"/>
-      <x:c r="D301" s="16"/>
-      <x:c r="E301" s="16"/>
+      <x:c r="A301" s="26" t="n">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="B301" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C301" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D301" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E301" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F301" s="26"/>
       <x:c r="G301" s="26"/>
-      <x:c r="H301" s="16"/>
+      <x:c r="H301" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I301" s="16"/>
-      <x:c r="J301" s="25"/>
-      <x:c r="K301" s="16"/>
-      <x:c r="L301" s="16"/>
+      <x:c r="J301" s="39" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K301" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L301" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M301" s="16"/>
-      <x:c r="N301" s="16"/>
-      <x:c r="O301" s="16"/>
-      <x:c r="P301" s="16"/>
+      <x:c r="N301" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O301" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P301" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="302">
-      <x:c r="A302" s="26"/>
-      <x:c r="B302" s="16"/>
-      <x:c r="C302" s="16"/>
-      <x:c r="D302" s="16"/>
-      <x:c r="E302" s="16"/>
+      <x:c r="A302" s="26" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="B302" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C302" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D302" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E302" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F302" s="26"/>
       <x:c r="G302" s="26"/>
-      <x:c r="H302" s="16"/>
+      <x:c r="H302" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I302" s="16"/>
-      <x:c r="J302" s="25"/>
-      <x:c r="K302" s="16"/>
-      <x:c r="L302" s="16"/>
+      <x:c r="J302" s="39" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K302" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L302" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M302" s="16"/>
-      <x:c r="N302" s="16"/>
-      <x:c r="O302" s="16"/>
-      <x:c r="P302" s="16"/>
+      <x:c r="N302" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O302" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P302" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="303">
-      <x:c r="A303" s="26"/>
-      <x:c r="B303" s="16"/>
-      <x:c r="C303" s="16"/>
-      <x:c r="D303" s="16"/>
-      <x:c r="E303" s="16"/>
+      <x:c r="A303" s="26" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="B303" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C303" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D303" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E303" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F303" s="26"/>
       <x:c r="G303" s="26"/>
-      <x:c r="H303" s="16"/>
+      <x:c r="H303" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I303" s="16"/>
-      <x:c r="J303" s="25"/>
-      <x:c r="K303" s="16"/>
-      <x:c r="L303" s="16"/>
+      <x:c r="J303" s="39" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="K303" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L303" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M303" s="16"/>
-      <x:c r="N303" s="16"/>
-      <x:c r="O303" s="16"/>
-      <x:c r="P303" s="16"/>
+      <x:c r="N303" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O303" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P303" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="304">
-      <x:c r="A304" s="26"/>
-      <x:c r="B304" s="16"/>
-      <x:c r="C304" s="16"/>
-      <x:c r="D304" s="16"/>
-      <x:c r="E304" s="16"/>
+      <x:c r="A304" s="26" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="B304" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C304" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D304" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E304" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F304" s="26"/>
       <x:c r="G304" s="26"/>
-      <x:c r="H304" s="16"/>
+      <x:c r="H304" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I304" s="16"/>
-      <x:c r="J304" s="25"/>
-      <x:c r="K304" s="16"/>
-      <x:c r="L304" s="16"/>
+      <x:c r="J304" s="39"/>
+      <x:c r="K304" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L304" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M304" s="16"/>
-      <x:c r="N304" s="16"/>
-      <x:c r="O304" s="16"/>
-      <x:c r="P304" s="16"/>
+      <x:c r="N304" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O304" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P304" s="16" t="str">
+        <x:v>Não exibido no vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="305">
-      <x:c r="A305" s="26"/>
-      <x:c r="B305" s="16"/>
-      <x:c r="C305" s="16"/>
-      <x:c r="D305" s="16"/>
-      <x:c r="E305" s="16"/>
+      <x:c r="A305" s="26" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="B305" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C305" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D305" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E305" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F305" s="26"/>
       <x:c r="G305" s="26"/>
-      <x:c r="H305" s="16"/>
+      <x:c r="H305" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I305" s="16"/>
-      <x:c r="J305" s="25"/>
-      <x:c r="K305" s="16"/>
-      <x:c r="L305" s="16"/>
+      <x:c r="J305" s="39" t="n">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="K305" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L305" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M305" s="16"/>
-      <x:c r="N305" s="16"/>
-      <x:c r="O305" s="16"/>
-      <x:c r="P305" s="16"/>
+      <x:c r="N305" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O305" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P305" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="306">
-      <x:c r="A306" s="26"/>
-      <x:c r="B306" s="16"/>
-      <x:c r="C306" s="16"/>
-      <x:c r="D306" s="16"/>
-      <x:c r="E306" s="16"/>
+      <x:c r="A306" s="26" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="B306" s="16" t="str">
+        <x:v>SC</x:v>
+      </x:c>
+      <x:c r="C306" s="16" t="str">
+        <x:v>FLN</x:v>
+      </x:c>
+      <x:c r="D306" s="16" t="str">
+        <x:v>RS</x:v>
+      </x:c>
+      <x:c r="E306" s="16" t="str">
+        <x:v>POA</x:v>
+      </x:c>
       <x:c r="F306" s="26"/>
       <x:c r="G306" s="26"/>
-      <x:c r="H306" s="16"/>
+      <x:c r="H306" s="16" t="str">
+        <x:v>Histórico de preço</x:v>
+      </x:c>
       <x:c r="I306" s="16"/>
-      <x:c r="J306" s="25"/>
-      <x:c r="K306" s="16"/>
-      <x:c r="L306" s="16"/>
+      <x:c r="J306" s="39" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="K306" s="16" t="str">
+        <x:v>Menor preço diário exibido</x:v>
+      </x:c>
+      <x:c r="L306" s="16" t="str">
+        <x:v>Conforme Google Flights</x:v>
+      </x:c>
       <x:c r="M306" s="16"/>
-      <x:c r="N306" s="16"/>
-      <x:c r="O306" s="16"/>
-      <x:c r="P306" s="16"/>
+      <x:c r="N306" s="16" t="str">
+        <x:v>Google Flights</x:v>
+      </x:c>
+      <x:c r="O306" s="16" t="str">
+        <x:v>Vídeo enviado para transcrição</x:v>
+      </x:c>
+      <x:c r="P306" s="16" t="str">
+        <x:v>Transcrito do vídeo. Rota: Florianópolis (FLN) → Porto Alegre (POA).</x:v>
+      </x:c>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="26"/>
@@ -29519,6 +30979,11 @@
       <x:formula>ISNUMBER(SEARCH("Não exibido",P2))</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="P246:P306">
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>ISNUMBER(SEARCH("Não exibido",P246))</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="B2:B1000">
       <x:formula1>LISTAS!$A$2:$A$6</x:formula1>
@@ -29532,7 +30997,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re90750637d034bf5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra044f00ed0e6496f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30550,7 +32015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92755fdf65c444ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R559c05079eb5428b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
